--- a/youtube-uploader/upload_tracker.xlsx
+++ b/youtube-uploader/upload_tracker.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I158"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4574,21 +4574,21 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor</t>
+          <t>Skoda Slavia</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Skoda Slavia ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -4608,32 +4608,32 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 16:37:31</t>
+          <t>2026-09-17 12:31:41</t>
         </is>
       </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\01_Hero_Splendor\Hero_Splendor.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_91_Skoda_Slavia\Skoda_Slavia.mp4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Honda Shine</t>
+          <t>Skoda Kushaq</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda Shine ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Skoda Kushaq ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 16:38:10</t>
+          <t>2026-09-17 12:39:19</t>
         </is>
       </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\02_Honda_Shine\Honda_Shine.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_92_Skoda_Kushaq\Skoda_Kushaq.mp4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3</v>
+        <v>93</v>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Pulsar</t>
+          <t>Skoda Kodiaq</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Pulsar ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Skoda Kodiaq ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -4698,32 +4698,32 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:45:27</t>
+          <t>2026-09-19 03:44:15</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\03_Bajaj_Pulsar\Bajaj_Pulsar.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_93_Skoda_Kodiaq\Skoda_Kodiaq.mp4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>TVS Apache</t>
+          <t>Skoda Superb</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Apache ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Skoda Superb ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:46:05</t>
+          <t>2026-09-19 03:47:45</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\04_TVS_Apache\TVS_Apache.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_94_Skoda_Superb\Skoda_Superb.mp4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Hero HF Deluxe</t>
+          <t>MG Hector</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero HF Deluxe ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature MG Hector ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:46:42</t>
+          <t>2026-09-19 03:52:11</t>
         </is>
       </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\05_Hero_HF_Deluxe\Hero_HF_Deluxe.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_95_MG_Hector\MG_Hector.mp4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Classic 350</t>
+          <t>Hero Splendor</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Classic 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -4833,22 +4833,22 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:54:28</t>
+          <t>2026-09-08 16:37:31</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\06_Royal_Enfield_Classic_350\Royal_Enfield_Classic_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\01_Hero_Splendor\Hero_Splendor.mp4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Honda CB Unicorn</t>
+          <t>Honda Shine</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CB Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda Shine ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -4878,22 +4878,22 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:55:06</t>
+          <t>2026-09-08 16:38:10</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\07_Honda_CB_Unicorn\Honda_CB_Unicorn.mp4</t>
+          <t>video-editor\bike assembling niche\output\02_Honda_Shine\Honda_Shine.mp4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>TVS Raider</t>
+          <t>Bajaj Pulsar</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Raider ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Pulsar ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -4923,22 +4923,22 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 16:01:00</t>
+          <t>2026-09-08 20:45:27</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\08_TVS_Raider\TVS_Raider.mp4</t>
+          <t>video-editor\bike assembling niche\output\03_Bajaj_Pulsar\Bajaj_Pulsar.mp4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Platina</t>
+          <t>TVS Apache</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Platina ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Apache ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 00:27:54</t>
+          <t>2026-09-08 20:46:05</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\09_Bajaj_Platina\Bajaj_Platina.mp4</t>
+          <t>video-editor\bike assembling niche\output\04_TVS_Apache\TVS_Apache.mp4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Bullet 350</t>
+          <t>Hero HF Deluxe</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Bullet 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero HF Deluxe ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -5013,22 +5013,22 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 00:28:33</t>
+          <t>2026-09-08 20:46:42</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\10_Royal_Enfield_Bullet_350\Royal_Enfield_Bullet_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\05_Hero_HF_Deluxe\Hero_HF_Deluxe.mp4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Hunter 350</t>
+          <t>Royal Enfield Classic 350</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Hunter 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Classic 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -5058,22 +5058,22 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 09:19:36</t>
+          <t>2026-09-09 12:54:28</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\11_Royal_Enfield_Hunter_350\Royal_Enfield_Hunter_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\06_Royal_Enfield_Classic_350\Royal_Enfield_Classic_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Honda SP 125</t>
+          <t>Honda CB Unicorn</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda SP 125 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda CB Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 09:20:14</t>
+          <t>2026-09-09 12:55:06</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\12_Honda_SP_125\Honda_SP_125.mp4</t>
+          <t>video-editor\bike assembling niche\output\07_Honda_CB_Unicorn\Honda_CB_Unicorn.mp4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Hero Xtreme 125R</t>
+          <t>TVS Raider</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Xtreme 125R ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Raider ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:18:12</t>
+          <t>2026-09-09 16:01:00</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\13_Hero_Xtreme_125R\Hero_Xtreme_125R.mp4</t>
+          <t>video-editor\bike assembling niche\output\08_TVS_Raider\TVS_Raider.mp4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Honda Unicorn</t>
+          <t>Bajaj Platina</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Platina ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -5193,22 +5193,22 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:18:53</t>
+          <t>2026-09-10 00:27:54</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\14_Honda_Unicorn\Honda_Unicorn.mp4</t>
+          <t>video-editor\bike assembling niche\output\09_Bajaj_Platina\Bajaj_Platina.mp4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Hero Super Splendor</t>
+          <t>Royal Enfield Bullet 350</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Super Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Bullet 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:19:34</t>
+          <t>2026-09-10 00:28:33</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\15_Hero_Super_Splendor\Hero_Super_Splendor.mp4</t>
+          <t>video-editor\bike assembling niche\output\10_Royal_Enfield_Bullet_350\Royal_Enfield_Bullet_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Discover 125</t>
+          <t>Royal Enfield Hunter 350</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Discover 125 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Hunter 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -5283,22 +5283,22 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:20:12</t>
+          <t>2026-09-10 09:19:36</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\16_Bajaj_Discover_125\Bajaj_Discover_125.mp4</t>
+          <t>video-editor\bike assembling niche\output\11_Royal_Enfield_Hunter_350\Royal_Enfield_Hunter_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>TVS Sport</t>
+          <t>Honda SP 125</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Sport ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda SP 125 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -5328,22 +5328,22 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:36:37</t>
+          <t>2026-09-10 09:20:14</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\17_TVS_Sport\TVS_Sport.mp4</t>
+          <t>video-editor\bike assembling niche\output\12_Honda_SP_125\Honda_SP_125.mp4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>TVS Radeon</t>
+          <t>Hero Xtreme 125R</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Radeon ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Xtreme 125R ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -5373,22 +5373,22 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:47:19</t>
+          <t>2026-09-12 23:18:12</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\18_TVS_Radeon\TVS_Radeon.mp4</t>
+          <t>video-editor\bike assembling niche\output\13_Hero_Xtreme_125R\Hero_Xtreme_125R.mp4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Himalayan 450</t>
+          <t>Honda Unicorn</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Himalayan 450 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -5418,22 +5418,22 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:37:15</t>
+          <t>2026-09-12 23:18:53</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\19_Royal_Enfield_Himalayan_450\Royal_Enfield_Himalayan_450.mp4</t>
+          <t>video-editor\bike assembling niche\output\14_Honda_Unicorn\Honda_Unicorn.mp4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-15</t>
+          <t>Hero Super Splendor</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha MT-15 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Super Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -5463,32 +5463,32 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:37:53</t>
+          <t>2026-09-12 23:19:34</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\20_Yamaha_MT-15\Yamaha_MT-15.mp4</t>
+          <t>video-editor\bike assembling niche\output\15_Hero_Super_Splendor\Hero_Super_Splendor.mp4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>9999</v>
+        <v>16</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Pikachu Motorcycle Story</t>
+          <t>Bajaj Discover 125</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Pikachu Gets His Heart Broken… 💔🏍️ #shorts #asmr #pikarevz</t>
+          <t>Miniature Bajaj Discover 125 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -5508,22 +5508,22 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 03:42:52</t>
+          <t>2026-09-12 23:20:12</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>d:\Temp\yt automation\video-editor\output\Pikachu_Motorcycle_Story\Pikachu_Motorcycle_Story.mp4</t>
+          <t>video-editor\bike assembling niche\output\16_Bajaj_Discover_125\Bajaj_Discover_125.mp4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>TVS Sport</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Splendor Plus ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Sport ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -5553,22 +5553,22 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:16:48</t>
+          <t>2026-09-14 00:36:37</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\01_Hero_Splendor_Plus_master_vehicles_tracker\Hero_Splendor_Plus.mp4</t>
+          <t>video-editor\bike assembling niche\output\17_TVS_Sport\TVS_Sport.mp4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>TVS Radeon</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha RX100 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Radeon ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -5598,22 +5598,22 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:23:04</t>
+          <t>2026-09-14 00:47:19</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\02_Yamaha_RX100_master_vehicles_tracker\Yamaha_RX100.mp4</t>
+          <t>video-editor\bike assembling niche\output\18_TVS_Radeon\TVS_Radeon.mp4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Royal Enfield Himalayan 450</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Ninja H2R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Himalayan 450 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -5643,37 +5643,37 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:23:56</t>
+          <t>2026-09-14 00:37:15</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\04_Kawasaki_Ninja_H2R_master_vehicles_tracker\Kawasaki_Ninja_H2R.mp4</t>
+          <t>video-editor\bike assembling niche\output\19_Royal_Enfield_Himalayan_450\Royal_Enfield_Himalayan_450.mp4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Yamaha MT-15</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Miniature Porsche 911 GT3 RS ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha MT-15 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>https://youtu.be/N6dhTj3t2CQ</t>
+          <t>https://studio.youtube.com/channel/videos/short</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -5688,32 +5688,32 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:28:00</t>
+          <t>2026-09-14 00:37:53</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\05_Porsche_911_GT3_RS_master_vehicles_tracker\Porsche_911_GT3_RS.mp4</t>
+          <t>video-editor\bike assembling niche\output\20_Yamaha_MT-15\Yamaha_MT-15.mp4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6</v>
+        <v>9999</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Pikachu Motorcycle Story</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ford Mustang 1969 Boss 429 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Pikachu Gets His Heart Broken… 💔🏍️ #shorts #asmr #pikarevz</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -5733,32 +5733,32 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:31:55</t>
+          <t>2026-09-10 03:42:52</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\06_Ford_Mustang_1969_Boss_429_master_vehicles_tracker\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>d:\Temp\yt automation\video-editor\output\Pikachu_Motorcycle_Story\Pikachu_Motorcycle_Story.mp4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Miniature Nissan Skyline GT-R R34 V-Spec II ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Hero Splendor Plus ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -5778,32 +5778,32 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:36:03</t>
+          <t>2026-09-06 16:16:48</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\07_Nissan_Skyline_GT-R_R34_V-Spec_II_master_vehicles_tracker\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>video-editor\output\01_Hero_Splendor_Plus_master_vehicles_tracker\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Aventador SVJ ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha RX100 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -5823,22 +5823,22 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:40:00</t>
+          <t>2026-09-06 16:23:04</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\08_Lamborghini_Aventador_SVJ_master_vehicles_tracker\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>video-editor\output\02_Yamaha_RX100_master_vehicles_tracker\Yamaha_RX100.mp4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ducati Panigale V4 S ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Kawasaki Ninja H2R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -5868,22 +5868,22 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:42:24</t>
+          <t>2026-09-06 16:23:56</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\09_Ducati_Panigale_V4_S_master_vehicles_tracker\Ducati_Panigale_V4_S.mp4</t>
+          <t>video-editor\output\04_Kawasaki_Ninja_H2R_master_vehicles_tracker\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Miniature Rolls Royce Phantom VIII ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Porsche 911 GT3 RS ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/channel/videos/short</t>
+          <t>https://youtu.be/N6dhTj3t2CQ</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5913,32 +5913,32 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:21</t>
+          <t>2026-09-06 16:28:00</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\10_Rolls_Royce_Phantom_VIII_master_vehicles_tracker\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>video-editor\output\05_Porsche_911_GT3_RS_master_vehicles_tracker\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Miniature BMW S1000RR M Package ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ford Mustang 1969 Boss 429 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:22</t>
+          <t>2026-09-06 16:31:55</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\11_BMW_S1000RR_M_Package_master_vehicles_tracker\BMW_S1000RR_M_Package.mp4</t>
+          <t>video-editor\output\06_Ford_Mustang_1969_Boss_429_master_vehicles_tracker\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Miniature Toyota Supra MK4 Turbo (A80) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Nissan Skyline GT-R R34 V-Spec II ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -6003,32 +6003,32 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:20</t>
+          <t>2026-09-06 16:36:03</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\12_Toyota_Supra_MK4_Turbo_(A80)_master_vehicles_tracker\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>video-editor\output\07_Nissan_Skyline_GT-R_R34_V-Spec_II_master_vehicles_tracker\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Miniature Suzuki Hayabusa GSX1300R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Lamborghini Aventador SVJ ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:58:15</t>
+          <t>2026-09-06 16:40:00</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\13_Suzuki_Hayabusa_GSX1300R_master_vehicles_tracker\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>video-editor\output\08_Lamborghini_Aventador_SVJ_master_vehicles_tracker\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ferrari F40 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Ducati Panigale V4 S ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -6093,32 +6093,32 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:05:25</t>
+          <t>2026-09-06 16:42:24</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\14_Ferrari_F40_master_vehicles_tracker\Ferrari_F40.mp4</t>
+          <t>video-editor\output\09_Ducati_Panigale_V4_S_master_vehicles_tracker\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Miniature Harley-Davidson Fat Boy 114 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Rolls Royce Phantom VIII ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -6138,32 +6138,32 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:07:44</t>
+          <t>2026-09-06 16:46:21</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\15_Harley-Davidson_Fat_Boy_114_master_vehicles_tracker\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>video-editor\output\10_Rolls_Royce_Phantom_VIII_master_vehicles_tracker\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Miniature McLaren P1 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature BMW S1000RR M Package ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -6183,32 +6183,32 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:10:01</t>
+          <t>2026-09-06 16:50:22</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\16_McLaren_P1_master_vehicles_tracker\McLaren_P1.mp4</t>
+          <t>video-editor\output\11_BMW_S1000RR_M_Package_master_vehicles_tracker\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Miniature KTM 390 Duke ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Toyota Supra MK4 Turbo (A80) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -6228,32 +6228,32 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:12:21</t>
+          <t>2026-09-06 16:54:20</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\17_KTM_390_Duke_master_vehicles_tracker\KTM_390_Duke.mp4</t>
+          <t>video-editor\output\12_Toyota_Supra_MK4_Turbo_(A80)_master_vehicles_tracker\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Miniature Dodge Challenger SRT Demon 170 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Suzuki Hayabusa GSX1300R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -6273,32 +6273,32 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 23:27:14</t>
+          <t>2026-09-06 16:58:15</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\18_Dodge_Challenger_SRT_Demon_170_master_vehicles_tracker\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>video-editor\output\13_Suzuki_Hayabusa_GSX1300R_master_vehicles_tracker\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha YZF-R1M ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ferrari F40 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -6318,32 +6318,32 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:51:55</t>
+          <t>2026-09-06 21:05:25</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>video-editor\output\14_Ferrari_F40_master_vehicles_tracker\Ferrari_F40.mp4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Miniature Mercedes-AMG G63 Brabus 800 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Harley-Davidson Fat Boy 114 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -6363,22 +6363,22 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:52:42</t>
+          <t>2026-09-06 21:07:44</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>video-editor\output\15_Harley-Davidson_Fat_Boy_114_master_vehicles_tracker\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bugatti Chiron Super Sport 300+ ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature McLaren P1 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:53:30</t>
+          <t>2026-09-06 21:10:01</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>video-editor\output\16_McLaren_P1_master_vehicles_tracker\McLaren_P1.mp4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Ninja ZX-10R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature KTM 390 Duke ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:59:11</t>
+          <t>2026-09-06 21:12:21</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>video-editor\output\17_KTM_390_Duke_master_vehicles_tracker\KTM_390_Duke.mp4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Miniature Triumph Rocket 3 R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Dodge Challenger SRT Demon 170 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -6498,32 +6498,32 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:17:15</t>
+          <t>2026-09-06 23:27:14</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>video-editor\output\18_Dodge_Challenger_SRT_Demon_170_master_vehicles_tracker\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Huracan STO ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha YZF-R1M ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -6543,32 +6543,32 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:22:07</t>
+          <t>2026-09-07 02:51:55</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Miniature MV Agusta Superveloce 800 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Mercedes-AMG G63 Brabus 800 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -6588,22 +6588,22 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:27:12</t>
+          <t>2026-09-07 02:52:42</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Miniature Pagani Huayra BC ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Bugatti Chiron Super Sport 300+ ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -6633,22 +6633,22 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:32:07</t>
+          <t>2026-09-07 02:53:30</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Miniature Aprilia RSV4 Factory 1100 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Kawasaki Ninja ZX-10R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -6678,32 +6678,32 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:57</t>
+          <t>2026-09-07 02:59:11</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Miniature Chevrolet Corvette Z06 (C8) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Triumph Rocket 3 R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -6723,32 +6723,32 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:23:04</t>
+          <t>2026-09-07 13:17:15</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CBR1000RR-R Fireblade SP ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Lamborghini Huracan STO ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -6768,32 +6768,32 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:28:58</t>
+          <t>2026-09-07 13:22:07</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Miniature Nissan GT-R Nismo (R35) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature MV Agusta Superveloce 800 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -6813,32 +6813,32 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:31:30</t>
+          <t>2026-09-07 13:27:12</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Miniature BMW M1000RR ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Pagani Huayra BC ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -6858,32 +6858,32 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:50:24</t>
+          <t>2026-09-07 13:32:07</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ferrari LaFerrari ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Aprilia RSV4 Factory 1100 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -6903,32 +6903,32 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:58:43</t>
+          <t>2026-09-07 13:36:57</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Miniature KTM 1290 Super Duke R Evo ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Chevrolet Corvette Z06 (C8) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -6948,32 +6948,32 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:14:49</t>
+          <t>2026-09-07 14:23:04</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Miniature Porsche 918 Spyder ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Honda CBR1000RR-R Fireblade SP ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -6993,32 +6993,32 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:25:34</t>
+          <t>2026-09-07 14:28:58</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Miniature Harley-Davidson Sportster S ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Nissan GT-R Nismo (R35) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:59:19</t>
+          <t>2026-09-07 14:31:30</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Miniature Shelby Cobra 427 S/C ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature BMW M1000RR ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -7083,32 +7083,32 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:00:12</t>
+          <t>2026-09-07 15:50:24</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ducati Diavel V4 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ferrari LaFerrari ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -7128,32 +7128,32 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:00:58</t>
+          <t>2026-09-07 15:58:43</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Miniature Audi R8 V10 Performance ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature KTM 1290 Super Duke R Evo ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -7173,32 +7173,32 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:01:43</t>
+          <t>2026-09-07 21:14:49</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha MT-10 SP ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Porsche 918 Spyder ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -7218,32 +7218,32 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:02:31</t>
+          <t>2026-09-07 21:25:34</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Miniature Mazda RX-7 Spirit R (FD3S) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Harley-Davidson Sportster S ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -7263,32 +7263,32 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:04:41</t>
+          <t>2026-09-07 21:59:19</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Z H2 Supercharged ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Shelby Cobra 427 S/C ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -7308,32 +7308,32 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:05:26</t>
+          <t>2026-09-07 22:00:12</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lexus LFA Nurburgring Edition ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Ducati Diavel V4 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -7353,32 +7353,32 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:06:21</t>
+          <t>2026-09-07 22:00:58</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Miniature Suzuki Katana ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Audi R8 V10 Performance ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -7398,32 +7398,32 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:07:11</t>
+          <t>2026-09-07 22:01:43</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Miniature McLaren 720S Spider ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha MT-10 SP ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:07:58</t>
+          <t>2026-09-07 22:02:31</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CB1000R Black Edition ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Mazda RX-7 Spirit R (FD3S) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -7488,32 +7488,32 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:32:57</t>
+          <t>2026-09-07 22:04:41</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Murcielago LP670-4 SV ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Kawasaki Z H2 Supercharged ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -7533,55 +7533,280 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:33:48</t>
+          <t>2026-09-07 22:05:26</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>Lexus LFA Nurburgring Edition</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Lexus LFA Nurburgring Edition ASMR Unboxing 🏎️ #shorts #cars</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:06:21</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>Suzuki Katana</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Suzuki Katana ASMR Unboxing 🏍️ #shorts #bikes</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:07:11</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>McLaren 720S Spider</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Miniature McLaren 720S Spider ASMR Unboxing 🏎️ #shorts #cars</t>
+        </is>
+      </c>
+      <c r="E160" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:07:58</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Honda CB1000R Black Edition ASMR Unboxing 🏍️ #shorts #bikes</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:32:57</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Lamborghini Murcielago LP670-4 SV ASMR Unboxing 🏎️ #shorts #cars</t>
+        </is>
+      </c>
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:33:48</t>
+        </is>
+      </c>
+      <c r="I162" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B163" s="3" t="inlineStr">
         <is>
           <t>Indian Scout Bobber</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
         <is>
           <t>Motorcycle</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D163" s="3" t="inlineStr">
         <is>
           <t>Miniature Indian Scout Bobber ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>https://studio.youtube.com/channel/videos/short</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>UPLOADED</t>
-        </is>
-      </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>2026-09-07 22:34:33</t>
         </is>
       </c>
-      <c r="I158" s="3" t="inlineStr">
+      <c r="I163" s="3" t="inlineStr">
         <is>
           <t>video-editor\output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
         </is>
@@ -7746,6 +7971,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E156" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId162"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/youtube-uploader/upload_tracker.xlsx
+++ b/youtube-uploader/upload_tracker.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4799,21 +4799,21 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor</t>
+          <t>MG Astor</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature MG Astor ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -4833,32 +4833,32 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 16:37:31</t>
+          <t>2026-09-20 00:52:00</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\01_Hero_Splendor\Hero_Splendor.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_96_MG_Astor\MG_Astor.mp4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>2</v>
+        <v>97</v>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Honda Shine</t>
+          <t>Mahindra Scorpio Classic</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda Shine ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Mahindra Scorpio Classic ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -4878,32 +4878,32 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 16:38:10</t>
+          <t>2026-09-20 00:58:00</t>
         </is>
       </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\02_Honda_Shine\Honda_Shine.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_97_Mahindra_Scorpio_Classic\Mahindra_Scorpio_Classic.mp4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3</v>
+        <v>98</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Pulsar</t>
+          <t>Hyundai Grand i10 Nios</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Pulsar ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hyundai Grand i10 Nios ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -4923,22 +4923,22 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:45:27</t>
+          <t>2026-09-20 01:01:21</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\03_Bajaj_Pulsar\Bajaj_Pulsar.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_98_Hyundai_Grand_i10_Nios\Hyundai_Grand_i10_Nios.mp4</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>TVS Apache</t>
+          <t>Hero Splendor</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Apache ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -4968,22 +4968,22 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:46:05</t>
+          <t>2026-09-08 16:37:31</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\04_TVS_Apache\TVS_Apache.mp4</t>
+          <t>video-editor\bike assembling niche\output\01_Hero_Splendor\Hero_Splendor.mp4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Hero HF Deluxe</t>
+          <t>Honda Shine</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero HF Deluxe ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda Shine ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -5013,22 +5013,22 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:46:42</t>
+          <t>2026-09-08 16:38:10</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\05_Hero_HF_Deluxe\Hero_HF_Deluxe.mp4</t>
+          <t>video-editor\bike assembling niche\output\02_Honda_Shine\Honda_Shine.mp4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Classic 350</t>
+          <t>Bajaj Pulsar</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Classic 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Pulsar ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -5058,22 +5058,22 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:54:28</t>
+          <t>2026-09-08 20:45:27</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\06_Royal_Enfield_Classic_350\Royal_Enfield_Classic_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\03_Bajaj_Pulsar\Bajaj_Pulsar.mp4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Honda CB Unicorn</t>
+          <t>TVS Apache</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CB Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Apache ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:55:06</t>
+          <t>2026-09-08 20:46:05</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\07_Honda_CB_Unicorn\Honda_CB_Unicorn.mp4</t>
+          <t>video-editor\bike assembling niche\output\04_TVS_Apache\TVS_Apache.mp4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>TVS Raider</t>
+          <t>Hero HF Deluxe</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Raider ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero HF Deluxe ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 16:01:00</t>
+          <t>2026-09-08 20:46:42</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\08_TVS_Raider\TVS_Raider.mp4</t>
+          <t>video-editor\bike assembling niche\output\05_Hero_HF_Deluxe\Hero_HF_Deluxe.mp4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Platina</t>
+          <t>Royal Enfield Classic 350</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Platina ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Classic 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -5193,22 +5193,22 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 00:27:54</t>
+          <t>2026-09-09 12:54:28</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\09_Bajaj_Platina\Bajaj_Platina.mp4</t>
+          <t>video-editor\bike assembling niche\output\06_Royal_Enfield_Classic_350\Royal_Enfield_Classic_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Bullet 350</t>
+          <t>Honda CB Unicorn</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Bullet 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda CB Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 00:28:33</t>
+          <t>2026-09-09 12:55:06</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\10_Royal_Enfield_Bullet_350\Royal_Enfield_Bullet_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\07_Honda_CB_Unicorn\Honda_CB_Unicorn.mp4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Hunter 350</t>
+          <t>TVS Raider</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Hunter 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Raider ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -5283,22 +5283,22 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 09:19:36</t>
+          <t>2026-09-09 16:01:00</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\11_Royal_Enfield_Hunter_350\Royal_Enfield_Hunter_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\08_TVS_Raider\TVS_Raider.mp4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Honda SP 125</t>
+          <t>Bajaj Platina</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda SP 125 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Platina ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -5328,22 +5328,22 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 09:20:14</t>
+          <t>2026-09-10 00:27:54</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\12_Honda_SP_125\Honda_SP_125.mp4</t>
+          <t>video-editor\bike assembling niche\output\09_Bajaj_Platina\Bajaj_Platina.mp4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Hero Xtreme 125R</t>
+          <t>Royal Enfield Bullet 350</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Xtreme 125R ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Bullet 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -5373,22 +5373,22 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:18:12</t>
+          <t>2026-09-10 00:28:33</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\13_Hero_Xtreme_125R\Hero_Xtreme_125R.mp4</t>
+          <t>video-editor\bike assembling niche\output\10_Royal_Enfield_Bullet_350\Royal_Enfield_Bullet_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Honda Unicorn</t>
+          <t>Royal Enfield Hunter 350</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Hunter 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -5418,22 +5418,22 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:18:53</t>
+          <t>2026-09-10 09:19:36</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\14_Honda_Unicorn\Honda_Unicorn.mp4</t>
+          <t>video-editor\bike assembling niche\output\11_Royal_Enfield_Hunter_350\Royal_Enfield_Hunter_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Hero Super Splendor</t>
+          <t>Honda SP 125</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Super Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda SP 125 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -5463,22 +5463,22 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:19:34</t>
+          <t>2026-09-10 09:20:14</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\15_Hero_Super_Splendor\Hero_Super_Splendor.mp4</t>
+          <t>video-editor\bike assembling niche\output\12_Honda_SP_125\Honda_SP_125.mp4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Discover 125</t>
+          <t>Hero Xtreme 125R</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Discover 125 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Xtreme 125R ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -5508,22 +5508,22 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:20:12</t>
+          <t>2026-09-12 23:18:12</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\16_Bajaj_Discover_125\Bajaj_Discover_125.mp4</t>
+          <t>video-editor\bike assembling niche\output\13_Hero_Xtreme_125R\Hero_Xtreme_125R.mp4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>TVS Sport</t>
+          <t>Honda Unicorn</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Sport ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -5553,22 +5553,22 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:36:37</t>
+          <t>2026-09-12 23:18:53</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\17_TVS_Sport\TVS_Sport.mp4</t>
+          <t>video-editor\bike assembling niche\output\14_Honda_Unicorn\Honda_Unicorn.mp4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>TVS Radeon</t>
+          <t>Hero Super Splendor</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Radeon ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Super Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -5598,22 +5598,22 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:47:19</t>
+          <t>2026-09-12 23:19:34</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\18_TVS_Radeon\TVS_Radeon.mp4</t>
+          <t>video-editor\bike assembling niche\output\15_Hero_Super_Splendor\Hero_Super_Splendor.mp4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Himalayan 450</t>
+          <t>Bajaj Discover 125</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Himalayan 450 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Discover 125 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -5643,22 +5643,22 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:37:15</t>
+          <t>2026-09-12 23:20:12</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\19_Royal_Enfield_Himalayan_450\Royal_Enfield_Himalayan_450.mp4</t>
+          <t>video-editor\bike assembling niche\output\16_Bajaj_Discover_125\Bajaj_Discover_125.mp4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-15</t>
+          <t>TVS Sport</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha MT-15 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Sport ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -5688,32 +5688,32 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:37:53</t>
+          <t>2026-09-14 00:36:37</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\20_Yamaha_MT-15\Yamaha_MT-15.mp4</t>
+          <t>video-editor\bike assembling niche\output\17_TVS_Sport\TVS_Sport.mp4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>9999</v>
+        <v>18</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Pikachu Motorcycle Story</t>
+          <t>TVS Radeon</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Pikachu Gets His Heart Broken… 💔🏍️ #shorts #asmr #pikarevz</t>
+          <t>Miniature TVS Radeon ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -5733,22 +5733,22 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 03:42:52</t>
+          <t>2026-09-14 00:47:19</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>d:\Temp\yt automation\video-editor\output\Pikachu_Motorcycle_Story\Pikachu_Motorcycle_Story.mp4</t>
+          <t>video-editor\bike assembling niche\output\18_TVS_Radeon\TVS_Radeon.mp4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>Royal Enfield Himalayan 450</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Splendor Plus ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Himalayan 450 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -5778,22 +5778,22 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:16:48</t>
+          <t>2026-09-14 00:37:15</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\01_Hero_Splendor_Plus_master_vehicles_tracker\Hero_Splendor_Plus.mp4</t>
+          <t>video-editor\bike assembling niche\output\19_Royal_Enfield_Himalayan_450\Royal_Enfield_Himalayan_450.mp4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Yamaha MT-15</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha RX100 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Yamaha MT-15 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -5823,32 +5823,32 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:23:04</t>
+          <t>2026-09-14 00:37:53</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\02_Yamaha_RX100_master_vehicles_tracker\Yamaha_RX100.mp4</t>
+          <t>video-editor\bike assembling niche\output\20_Yamaha_MT-15\Yamaha_MT-15.mp4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>4</v>
+        <v>9999</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Pikachu Motorcycle Story</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Ninja H2R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Pikachu Gets His Heart Broken… 💔🏍️ #shorts #asmr #pikarevz</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -5868,37 +5868,37 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:23:56</t>
+          <t>2026-09-10 03:42:52</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\04_Kawasaki_Ninja_H2R_master_vehicles_tracker\Kawasaki_Ninja_H2R.mp4</t>
+          <t>d:\Temp\yt automation\video-editor\output\Pikachu_Motorcycle_Story\Pikachu_Motorcycle_Story.mp4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Miniature Porsche 911 GT3 RS ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Hero Splendor Plus ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>https://youtu.be/N6dhTj3t2CQ</t>
+          <t>https://studio.youtube.com/channel/videos/short</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -5913,32 +5913,32 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:28:00</t>
+          <t>2026-09-06 16:16:48</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\05_Porsche_911_GT3_RS_master_vehicles_tracker\Porsche_911_GT3_RS.mp4</t>
+          <t>video-editor\output\01_Hero_Splendor_Plus_master_vehicles_tracker\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ford Mustang 1969 Boss 429 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha RX100 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -5958,32 +5958,32 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:31:55</t>
+          <t>2026-09-06 16:23:04</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\06_Ford_Mustang_1969_Boss_429_master_vehicles_tracker\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>video-editor\output\02_Yamaha_RX100_master_vehicles_tracker\Yamaha_RX100.mp4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Miniature Nissan Skyline GT-R R34 V-Spec II ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Kawasaki Ninja H2R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:36:03</t>
+          <t>2026-09-06 16:23:56</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\07_Nissan_Skyline_GT-R_R34_V-Spec_II_master_vehicles_tracker\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>video-editor\output\04_Kawasaki_Ninja_H2R_master_vehicles_tracker\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Aventador SVJ ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Porsche 911 GT3 RS ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/channel/videos/short</t>
+          <t>https://youtu.be/N6dhTj3t2CQ</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:40:00</t>
+          <t>2026-09-06 16:28:00</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\08_Lamborghini_Aventador_SVJ_master_vehicles_tracker\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>video-editor\output\05_Porsche_911_GT3_RS_master_vehicles_tracker\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ducati Panigale V4 S ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ford Mustang 1969 Boss 429 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -6093,22 +6093,22 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:42:24</t>
+          <t>2026-09-06 16:31:55</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\09_Ducati_Panigale_V4_S_master_vehicles_tracker\Ducati_Panigale_V4_S.mp4</t>
+          <t>video-editor\output\06_Ford_Mustang_1969_Boss_429_master_vehicles_tracker\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Miniature Rolls Royce Phantom VIII ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Nissan Skyline GT-R R34 V-Spec II ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -6138,32 +6138,32 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:21</t>
+          <t>2026-09-06 16:36:03</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\10_Rolls_Royce_Phantom_VIII_master_vehicles_tracker\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>video-editor\output\07_Nissan_Skyline_GT-R_R34_V-Spec_II_master_vehicles_tracker\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Miniature BMW S1000RR M Package ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Lamborghini Aventador SVJ ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -6183,32 +6183,32 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:22</t>
+          <t>2026-09-06 16:40:00</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\11_BMW_S1000RR_M_Package_master_vehicles_tracker\BMW_S1000RR_M_Package.mp4</t>
+          <t>video-editor\output\08_Lamborghini_Aventador_SVJ_master_vehicles_tracker\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Miniature Toyota Supra MK4 Turbo (A80) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Ducati Panigale V4 S ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -6228,32 +6228,32 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:20</t>
+          <t>2026-09-06 16:42:24</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\12_Toyota_Supra_MK4_Turbo_(A80)_master_vehicles_tracker\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>video-editor\output\09_Ducati_Panigale_V4_S_master_vehicles_tracker\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Miniature Suzuki Hayabusa GSX1300R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Rolls Royce Phantom VIII ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -6273,32 +6273,32 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:58:15</t>
+          <t>2026-09-06 16:46:21</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\13_Suzuki_Hayabusa_GSX1300R_master_vehicles_tracker\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>video-editor\output\10_Rolls_Royce_Phantom_VIII_master_vehicles_tracker\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ferrari F40 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature BMW S1000RR M Package ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -6318,32 +6318,32 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:05:25</t>
+          <t>2026-09-06 16:50:22</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\14_Ferrari_F40_master_vehicles_tracker\Ferrari_F40.mp4</t>
+          <t>video-editor\output\11_BMW_S1000RR_M_Package_master_vehicles_tracker\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Miniature Harley-Davidson Fat Boy 114 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Toyota Supra MK4 Turbo (A80) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -6363,32 +6363,32 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:07:44</t>
+          <t>2026-09-06 16:54:20</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\15_Harley-Davidson_Fat_Boy_114_master_vehicles_tracker\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>video-editor\output\12_Toyota_Supra_MK4_Turbo_(A80)_master_vehicles_tracker\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Miniature McLaren P1 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Suzuki Hayabusa GSX1300R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -6408,32 +6408,32 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:10:01</t>
+          <t>2026-09-06 16:58:15</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\16_McLaren_P1_master_vehicles_tracker\McLaren_P1.mp4</t>
+          <t>video-editor\output\13_Suzuki_Hayabusa_GSX1300R_master_vehicles_tracker\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Miniature KTM 390 Duke ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ferrari F40 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:12:21</t>
+          <t>2026-09-06 21:05:25</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\17_KTM_390_Duke_master_vehicles_tracker\KTM_390_Duke.mp4</t>
+          <t>video-editor\output\14_Ferrari_F40_master_vehicles_tracker\Ferrari_F40.mp4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Miniature Dodge Challenger SRT Demon 170 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Harley-Davidson Fat Boy 114 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -6498,32 +6498,32 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 23:27:14</t>
+          <t>2026-09-06 21:07:44</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\18_Dodge_Challenger_SRT_Demon_170_master_vehicles_tracker\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>video-editor\output\15_Harley-Davidson_Fat_Boy_114_master_vehicles_tracker\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha YZF-R1M ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature McLaren P1 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -6543,32 +6543,32 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:51:55</t>
+          <t>2026-09-06 21:10:01</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>video-editor\output\16_McLaren_P1_master_vehicles_tracker\McLaren_P1.mp4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Miniature Mercedes-AMG G63 Brabus 800 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature KTM 390 Duke ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -6588,22 +6588,22 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:52:42</t>
+          <t>2026-09-06 21:12:21</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>video-editor\output\17_KTM_390_Duke_master_vehicles_tracker\KTM_390_Duke.mp4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bugatti Chiron Super Sport 300+ ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Dodge Challenger SRT Demon 170 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -6633,22 +6633,22 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:53:30</t>
+          <t>2026-09-06 23:27:14</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>video-editor\output\18_Dodge_Challenger_SRT_Demon_170_master_vehicles_tracker\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Ninja ZX-10R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Yamaha YZF-R1M ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -6678,32 +6678,32 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:59:11</t>
+          <t>2026-09-07 02:51:55</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Miniature Triumph Rocket 3 R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Mercedes-AMG G63 Brabus 800 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -6723,22 +6723,22 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:17:15</t>
+          <t>2026-09-07 02:52:42</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Huracan STO ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Bugatti Chiron Super Sport 300+ ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -6768,22 +6768,22 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:22:07</t>
+          <t>2026-09-07 02:53:30</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Miniature MV Agusta Superveloce 800 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Kawasaki Ninja ZX-10R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -6813,32 +6813,32 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:27:12</t>
+          <t>2026-09-07 02:59:11</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Miniature Pagani Huayra BC ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Triumph Rocket 3 R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -6858,32 +6858,32 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:32:07</t>
+          <t>2026-09-07 13:17:15</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Miniature Aprilia RSV4 Factory 1100 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Lamborghini Huracan STO ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -6903,32 +6903,32 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:57</t>
+          <t>2026-09-07 13:22:07</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Miniature Chevrolet Corvette Z06 (C8) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature MV Agusta Superveloce 800 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -6948,32 +6948,32 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:23:04</t>
+          <t>2026-09-07 13:27:12</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CBR1000RR-R Fireblade SP ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Pagani Huayra BC ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -6993,32 +6993,32 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:28:58</t>
+          <t>2026-09-07 13:32:07</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Miniature Nissan GT-R Nismo (R35) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Aprilia RSV4 Factory 1100 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -7038,32 +7038,32 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:31:30</t>
+          <t>2026-09-07 13:36:57</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Miniature BMW M1000RR ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Chevrolet Corvette Z06 (C8) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -7083,32 +7083,32 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:50:24</t>
+          <t>2026-09-07 14:23:04</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ferrari LaFerrari ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Honda CBR1000RR-R Fireblade SP ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -7128,32 +7128,32 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:58:43</t>
+          <t>2026-09-07 14:28:58</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Miniature KTM 1290 Super Duke R Evo ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Nissan GT-R Nismo (R35) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -7173,32 +7173,32 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:14:49</t>
+          <t>2026-09-07 14:31:30</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Miniature Porsche 918 Spyder ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature BMW M1000RR ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -7218,32 +7218,32 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:25:34</t>
+          <t>2026-09-07 15:50:24</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Miniature Harley-Davidson Sportster S ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ferrari LaFerrari ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -7263,32 +7263,32 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:59:19</t>
+          <t>2026-09-07 15:58:43</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Miniature Shelby Cobra 427 S/C ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature KTM 1290 Super Duke R Evo ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -7308,32 +7308,32 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:00:12</t>
+          <t>2026-09-07 21:14:49</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ducati Diavel V4 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Porsche 918 Spyder ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -7353,32 +7353,32 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:00:58</t>
+          <t>2026-09-07 21:25:34</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Miniature Audi R8 V10 Performance ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Harley-Davidson Sportster S ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -7398,32 +7398,32 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:01:43</t>
+          <t>2026-09-07 21:59:19</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha MT-10 SP ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Shelby Cobra 427 S/C ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -7443,32 +7443,32 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:02:31</t>
+          <t>2026-09-07 22:00:12</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Miniature Mazda RX-7 Spirit R (FD3S) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Ducati Diavel V4 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -7488,32 +7488,32 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:04:41</t>
+          <t>2026-09-07 22:00:58</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Z H2 Supercharged ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Audi R8 V10 Performance ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -7533,32 +7533,32 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:05:26</t>
+          <t>2026-09-07 22:01:43</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lexus LFA Nurburgring Edition ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha MT-10 SP ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -7578,32 +7578,32 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:06:21</t>
+          <t>2026-09-07 22:02:31</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Miniature Suzuki Katana ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Mazda RX-7 Spirit R (FD3S) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:07:11</t>
+          <t>2026-09-07 22:04:41</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Miniature McLaren 720S Spider ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Kawasaki Z H2 Supercharged ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:07:58</t>
+          <t>2026-09-07 22:05:26</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CB1000R Black Edition ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Lexus LFA Nurburgring Edition ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -7713,32 +7713,32 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:32:57</t>
+          <t>2026-09-07 22:06:21</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Murcielago LP670-4 SV ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Suzuki Katana ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -7758,55 +7758,190 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:33:48</t>
+          <t>2026-09-07 22:07:11</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>McLaren 720S Spider</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Miniature McLaren 720S Spider ASMR Unboxing 🏎️ #shorts #cars</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:07:58</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Honda CB1000R Black Edition ASMR Unboxing 🏍️ #shorts #bikes</t>
+        </is>
+      </c>
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:32:57</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Lamborghini Murcielago LP670-4 SV ASMR Unboxing 🏎️ #shorts #cars</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:33:48</t>
+        </is>
+      </c>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>Indian Scout Bobber</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Motorcycle</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>Miniature Indian Scout Bobber ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>https://studio.youtube.com/channel/videos/short</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>UPLOADED</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>2026-09-07 22:34:33</t>
         </is>
       </c>
-      <c r="I163" s="3" t="inlineStr">
+      <c r="I166" s="3" t="inlineStr">
         <is>
           <t>video-editor\output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
         </is>
@@ -7976,6 +8111,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E161" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E162" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId165"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/youtube-uploader/upload_tracker.xlsx
+++ b/youtube-uploader/upload_tracker.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I166"/>
+  <dimension ref="A1:I168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4934,21 +4934,21 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor</t>
+          <t>MG ZS EV</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature MG ZS EV ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -4968,32 +4968,32 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 16:37:31</t>
+          <t>2026-09-21 00:13:42</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\01_Hero_Splendor\Hero_Splendor.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_99_MG_ZS_EV\MG_ZS_EV.mp4</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Honda Shine</t>
+          <t>Jeep Compass</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda Shine ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Jeep Compass ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -5013,22 +5013,22 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 16:38:10</t>
+          <t>2026-09-21 00:30:00</t>
         </is>
       </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\02_Honda_Shine\Honda_Shine.mp4</t>
+          <t>video-editor\output\100_popular_cars_in_India_100_Jeep_Compass\Jeep_Compass.mp4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Pulsar</t>
+          <t>Hero Splendor</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Pulsar ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
@@ -5058,22 +5058,22 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:45:27</t>
+          <t>2026-09-08 16:37:31</t>
         </is>
       </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\03_Bajaj_Pulsar\Bajaj_Pulsar.mp4</t>
+          <t>video-editor\bike assembling niche\output\01_Hero_Splendor\Hero_Splendor.mp4</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>TVS Apache</t>
+          <t>Honda Shine</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Apache ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda Shine ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:46:05</t>
+          <t>2026-09-08 16:38:10</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\04_TVS_Apache\TVS_Apache.mp4</t>
+          <t>video-editor\bike assembling niche\output\02_Honda_Shine\Honda_Shine.mp4</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Hero HF Deluxe</t>
+          <t>Bajaj Pulsar</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero HF Deluxe ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Pulsar ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08 20:46:42</t>
+          <t>2026-09-08 20:45:27</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\05_Hero_HF_Deluxe\Hero_HF_Deluxe.mp4</t>
+          <t>video-editor\bike assembling niche\output\03_Bajaj_Pulsar\Bajaj_Pulsar.mp4</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Classic 350</t>
+          <t>TVS Apache</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Classic 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Apache ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -5193,22 +5193,22 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:54:28</t>
+          <t>2026-09-08 20:46:05</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\06_Royal_Enfield_Classic_350\Royal_Enfield_Classic_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\04_TVS_Apache\TVS_Apache.mp4</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Honda CB Unicorn</t>
+          <t>Hero HF Deluxe</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CB Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero HF Deluxe ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -5238,22 +5238,22 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 12:55:06</t>
+          <t>2026-09-08 20:46:42</t>
         </is>
       </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\07_Honda_CB_Unicorn\Honda_CB_Unicorn.mp4</t>
+          <t>video-editor\bike assembling niche\output\05_Hero_HF_Deluxe\Hero_HF_Deluxe.mp4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>TVS Raider</t>
+          <t>Royal Enfield Classic 350</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Raider ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Classic 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -5283,22 +5283,22 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-09 16:01:00</t>
+          <t>2026-09-09 12:54:28</t>
         </is>
       </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\08_TVS_Raider\TVS_Raider.mp4</t>
+          <t>video-editor\bike assembling niche\output\06_Royal_Enfield_Classic_350\Royal_Enfield_Classic_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Platina</t>
+          <t>Honda CB Unicorn</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Platina ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda CB Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -5328,22 +5328,22 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 00:27:54</t>
+          <t>2026-09-09 12:55:06</t>
         </is>
       </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\09_Bajaj_Platina\Bajaj_Platina.mp4</t>
+          <t>video-editor\bike assembling niche\output\07_Honda_CB_Unicorn\Honda_CB_Unicorn.mp4</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Bullet 350</t>
+          <t>TVS Raider</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Bullet 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Raider ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -5373,22 +5373,22 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 00:28:33</t>
+          <t>2026-09-09 16:01:00</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\10_Royal_Enfield_Bullet_350\Royal_Enfield_Bullet_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\08_TVS_Raider\TVS_Raider.mp4</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Hunter 350</t>
+          <t>Bajaj Platina</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Hunter 350 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Platina ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -5418,22 +5418,22 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 09:19:36</t>
+          <t>2026-09-10 00:27:54</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\11_Royal_Enfield_Hunter_350\Royal_Enfield_Hunter_350.mp4</t>
+          <t>video-editor\bike assembling niche\output\09_Bajaj_Platina\Bajaj_Platina.mp4</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Honda SP 125</t>
+          <t>Royal Enfield Bullet 350</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda SP 125 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Bullet 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -5463,22 +5463,22 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 09:20:14</t>
+          <t>2026-09-10 00:28:33</t>
         </is>
       </c>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\12_Honda_SP_125\Honda_SP_125.mp4</t>
+          <t>video-editor\bike assembling niche\output\10_Royal_Enfield_Bullet_350\Royal_Enfield_Bullet_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Hero Xtreme 125R</t>
+          <t>Royal Enfield Hunter 350</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Xtreme 125R ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Royal Enfield Hunter 350 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -5508,22 +5508,22 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:18:12</t>
+          <t>2026-09-10 09:19:36</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\13_Hero_Xtreme_125R\Hero_Xtreme_125R.mp4</t>
+          <t>video-editor\bike assembling niche\output\11_Royal_Enfield_Hunter_350\Royal_Enfield_Hunter_350.mp4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Honda Unicorn</t>
+          <t>Honda SP 125</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda SP 125 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -5553,22 +5553,22 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:18:53</t>
+          <t>2026-09-10 09:20:14</t>
         </is>
       </c>
       <c r="I113" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\14_Honda_Unicorn\Honda_Unicorn.mp4</t>
+          <t>video-editor\bike assembling niche\output\12_Honda_SP_125\Honda_SP_125.mp4</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Hero Super Splendor</t>
+          <t>Hero Xtreme 125R</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Super Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Xtreme 125R ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -5598,22 +5598,22 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:19:34</t>
+          <t>2026-09-12 23:18:12</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\15_Hero_Super_Splendor\Hero_Super_Splendor.mp4</t>
+          <t>video-editor\bike assembling niche\output\13_Hero_Xtreme_125R\Hero_Xtreme_125R.mp4</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Bajaj Discover 125</t>
+          <t>Honda Unicorn</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bajaj Discover 125 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda Unicorn ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
@@ -5643,22 +5643,22 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12 23:20:12</t>
+          <t>2026-09-12 23:18:53</t>
         </is>
       </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\16_Bajaj_Discover_125\Bajaj_Discover_125.mp4</t>
+          <t>video-editor\bike assembling niche\output\14_Honda_Unicorn\Honda_Unicorn.mp4</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>TVS Sport</t>
+          <t>Hero Super Splendor</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Sport ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Super Splendor ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:36:37</t>
+          <t>2026-09-12 23:19:34</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\17_TVS_Sport\TVS_Sport.mp4</t>
+          <t>video-editor\bike assembling niche\output\15_Hero_Super_Splendor\Hero_Super_Splendor.mp4</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>TVS Radeon</t>
+          <t>Bajaj Discover 125</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Miniature TVS Radeon ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature Bajaj Discover 125 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -5733,22 +5733,22 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:47:19</t>
+          <t>2026-09-12 23:20:12</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\18_TVS_Radeon\TVS_Radeon.mp4</t>
+          <t>video-editor\bike assembling niche\output\16_Bajaj_Discover_125\Bajaj_Discover_125.mp4</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Royal Enfield Himalayan 450</t>
+          <t>TVS Sport</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Miniature Royal Enfield Himalayan 450 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Sport ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
@@ -5778,22 +5778,22 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:37:15</t>
+          <t>2026-09-14 00:36:37</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\19_Royal_Enfield_Himalayan_450\Royal_Enfield_Himalayan_450.mp4</t>
+          <t>video-editor\bike assembling niche\output\17_TVS_Sport\TVS_Sport.mp4</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-15</t>
+          <t>TVS Radeon</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha MT-15 ASMR Assembly 🏍️ #shorts #bikes</t>
+          <t>Miniature TVS Radeon ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
@@ -5823,32 +5823,32 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14 00:37:53</t>
+          <t>2026-09-14 00:47:19</t>
         </is>
       </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>video-editor\bike assembling niche\output\20_Yamaha_MT-15\Yamaha_MT-15.mp4</t>
+          <t>video-editor\bike assembling niche\output\18_TVS_Radeon\TVS_Radeon.mp4</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>9999</v>
+        <v>19</v>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Pikachu Motorcycle Story</t>
+          <t>Royal Enfield Himalayan 450</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Pikachu Gets His Heart Broken… 💔🏍️ #shorts #asmr #pikarevz</t>
+          <t>Miniature Royal Enfield Himalayan 450 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
@@ -5868,22 +5868,22 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10 03:42:52</t>
+          <t>2026-09-14 00:37:15</t>
         </is>
       </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
-          <t>d:\Temp\yt automation\video-editor\output\Pikachu_Motorcycle_Story\Pikachu_Motorcycle_Story.mp4</t>
+          <t>video-editor\bike assembling niche\output\19_Royal_Enfield_Himalayan_450\Royal_Enfield_Himalayan_450.mp4</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Hero Splendor Plus</t>
+          <t>Yamaha MT-15</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Miniature Hero Splendor Plus ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Yamaha MT-15 ASMR Assembly 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -5913,32 +5913,32 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:16:48</t>
+          <t>2026-09-14 00:37:53</t>
         </is>
       </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\01_Hero_Splendor_Plus_master_vehicles_tracker\Hero_Splendor_Plus.mp4</t>
+          <t>video-editor\bike assembling niche\output\20_Yamaha_MT-15\Yamaha_MT-15.mp4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>2</v>
+        <v>9999</v>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Yamaha RX100</t>
+          <t>Pikachu Motorcycle Story</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha RX100 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Pikachu Gets His Heart Broken… 💔🏍️ #shorts #asmr #pikarevz</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:23:04</t>
+          <t>2026-09-10 03:42:52</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\02_Yamaha_RX100_master_vehicles_tracker\Yamaha_RX100.mp4</t>
+          <t>d:\Temp\yt automation\video-editor\output\Pikachu_Motorcycle_Story\Pikachu_Motorcycle_Story.mp4</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja H2R</t>
+          <t>Hero Splendor Plus</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Ninja H2R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Hero Splendor Plus ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
@@ -6003,37 +6003,37 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:23:56</t>
+          <t>2026-09-06 16:16:48</t>
         </is>
       </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\04_Kawasaki_Ninja_H2R_master_vehicles_tracker\Kawasaki_Ninja_H2R.mp4</t>
+          <t>video-editor\output\01_Hero_Splendor_Plus_master_vehicles_tracker\Hero_Splendor_Plus.mp4</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Porsche 911 GT3 RS</t>
+          <t>Yamaha RX100</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Miniature Porsche 911 GT3 RS ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha RX100 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>https://youtu.be/N6dhTj3t2CQ</t>
+          <t>https://studio.youtube.com/channel/videos/short</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:28:00</t>
+          <t>2026-09-06 16:23:04</t>
         </is>
       </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\05_Porsche_911_GT3_RS_master_vehicles_tracker\Porsche_911_GT3_RS.mp4</t>
+          <t>video-editor\output\02_Yamaha_RX100_master_vehicles_tracker\Yamaha_RX100.mp4</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Ford Mustang 1969 Boss 429</t>
+          <t>Kawasaki Ninja H2R</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ford Mustang 1969 Boss 429 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Kawasaki Ninja H2R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
@@ -6093,22 +6093,22 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:31:55</t>
+          <t>2026-09-06 16:23:56</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\06_Ford_Mustang_1969_Boss_429_master_vehicles_tracker\Ford_Mustang_1969_Boss_429.mp4</t>
+          <t>video-editor\output\04_Kawasaki_Ninja_H2R_master_vehicles_tracker\Kawasaki_Ninja_H2R.mp4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Nissan Skyline GT-R R34 V-Spec II</t>
+          <t>Porsche 911 GT3 RS</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Miniature Nissan Skyline GT-R R34 V-Spec II ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Porsche 911 GT3 RS ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>https://studio.youtube.com/channel/videos/short</t>
+          <t>https://youtu.be/N6dhTj3t2CQ</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -6138,22 +6138,22 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:36:03</t>
+          <t>2026-09-06 16:28:00</t>
         </is>
       </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\07_Nissan_Skyline_GT-R_R34_V-Spec_II_master_vehicles_tracker\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
+          <t>video-editor\output\05_Porsche_911_GT3_RS_master_vehicles_tracker\Porsche_911_GT3_RS.mp4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Aventador SVJ</t>
+          <t>Ford Mustang 1969 Boss 429</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Aventador SVJ ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Ford Mustang 1969 Boss 429 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
@@ -6183,32 +6183,32 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:40:00</t>
+          <t>2026-09-06 16:31:55</t>
         </is>
       </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\08_Lamborghini_Aventador_SVJ_master_vehicles_tracker\Lamborghini_Aventador_SVJ.mp4</t>
+          <t>video-editor\output\06_Ford_Mustang_1969_Boss_429_master_vehicles_tracker\Ford_Mustang_1969_Boss_429.mp4</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>Ducati Panigale V4 S</t>
+          <t>Nissan Skyline GT-R R34 V-Spec II</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ducati Panigale V4 S ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Nissan Skyline GT-R R34 V-Spec II ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
@@ -6228,22 +6228,22 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:42:24</t>
+          <t>2026-09-06 16:36:03</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\09_Ducati_Panigale_V4_S_master_vehicles_tracker\Ducati_Panigale_V4_S.mp4</t>
+          <t>video-editor\output\07_Nissan_Skyline_GT-R_R34_V-Spec_II_master_vehicles_tracker\Nissan_Skyline_GT-R_R34_V-Spec_II.mp4</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Rolls Royce Phantom VIII</t>
+          <t>Lamborghini Aventador SVJ</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Miniature Rolls Royce Phantom VIII ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Lamborghini Aventador SVJ ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
@@ -6273,22 +6273,22 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:46:21</t>
+          <t>2026-09-06 16:40:00</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\10_Rolls_Royce_Phantom_VIII_master_vehicles_tracker\Rolls_Royce_Phantom_VIII.mp4</t>
+          <t>video-editor\output\08_Lamborghini_Aventador_SVJ_master_vehicles_tracker\Lamborghini_Aventador_SVJ.mp4</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>BMW S1000RR M Package</t>
+          <t>Ducati Panigale V4 S</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Miniature BMW S1000RR M Package ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ducati Panigale V4 S ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
@@ -6318,22 +6318,22 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:50:22</t>
+          <t>2026-09-06 16:42:24</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\11_BMW_S1000RR_M_Package_master_vehicles_tracker\BMW_S1000RR_M_Package.mp4</t>
+          <t>video-editor\output\09_Ducati_Panigale_V4_S_master_vehicles_tracker\Ducati_Panigale_V4_S.mp4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Toyota Supra MK4 Turbo (A80)</t>
+          <t>Rolls Royce Phantom VIII</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -6343,7 +6343,7 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Miniature Toyota Supra MK4 Turbo (A80) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Rolls Royce Phantom VIII ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
@@ -6363,22 +6363,22 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:54:20</t>
+          <t>2026-09-06 16:46:21</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\12_Toyota_Supra_MK4_Turbo_(A80)_master_vehicles_tracker\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
+          <t>video-editor\output\10_Rolls_Royce_Phantom_VIII_master_vehicles_tracker\Rolls_Royce_Phantom_VIII.mp4</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Hayabusa GSX1300R</t>
+          <t>BMW S1000RR M Package</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Miniature Suzuki Hayabusa GSX1300R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature BMW S1000RR M Package ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:58:15</t>
+          <t>2026-09-06 16:50:22</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\13_Suzuki_Hayabusa_GSX1300R_master_vehicles_tracker\Suzuki_Hayabusa_GSX1300R.mp4</t>
+          <t>video-editor\output\11_BMW_S1000RR_M_Package_master_vehicles_tracker\BMW_S1000RR_M_Package.mp4</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Ferrari F40</t>
+          <t>Toyota Supra MK4 Turbo (A80)</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -6433,7 +6433,7 @@
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ferrari F40 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Toyota Supra MK4 Turbo (A80) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
@@ -6453,22 +6453,22 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:05:25</t>
+          <t>2026-09-06 16:54:20</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\14_Ferrari_F40_master_vehicles_tracker\Ferrari_F40.mp4</t>
+          <t>video-editor\output\12_Toyota_Supra_MK4_Turbo_(A80)_master_vehicles_tracker\Toyota_Supra_MK4_Turbo_(A80).mp4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Fat Boy 114</t>
+          <t>Suzuki Hayabusa GSX1300R</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Miniature Harley-Davidson Fat Boy 114 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Suzuki Hayabusa GSX1300R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -6498,22 +6498,22 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:07:44</t>
+          <t>2026-09-06 16:58:15</t>
         </is>
       </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\15_Harley-Davidson_Fat_Boy_114_master_vehicles_tracker\Harley-Davidson_Fat_Boy_114.mp4</t>
+          <t>video-editor\output\13_Suzuki_Hayabusa_GSX1300R_master_vehicles_tracker\Suzuki_Hayabusa_GSX1300R.mp4</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>McLaren P1</t>
+          <t>Ferrari F40</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Miniature McLaren P1 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Ferrari F40 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
@@ -6543,22 +6543,22 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:10:01</t>
+          <t>2026-09-06 21:05:25</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\16_McLaren_P1_master_vehicles_tracker\McLaren_P1.mp4</t>
+          <t>video-editor\output\14_Ferrari_F40_master_vehicles_tracker\Ferrari_F40.mp4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>KTM 390 Duke</t>
+          <t>Harley-Davidson Fat Boy 114</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Miniature KTM 390 Duke ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Harley-Davidson Fat Boy 114 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
@@ -6588,22 +6588,22 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 21:12:21</t>
+          <t>2026-09-06 21:07:44</t>
         </is>
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\17_KTM_390_Duke_master_vehicles_tracker\KTM_390_Duke.mp4</t>
+          <t>video-editor\output\15_Harley-Davidson_Fat_Boy_114_master_vehicles_tracker\Harley-Davidson_Fat_Boy_114.mp4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Dodge Challenger SRT Demon 170</t>
+          <t>McLaren P1</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>Miniature Dodge Challenger SRT Demon 170 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature McLaren P1 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
@@ -6633,22 +6633,22 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-06 23:27:14</t>
+          <t>2026-09-06 21:10:01</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\18_Dodge_Challenger_SRT_Demon_170_master_vehicles_tracker\Dodge_Challenger_SRT_Demon_170.mp4</t>
+          <t>video-editor\output\16_McLaren_P1_master_vehicles_tracker\McLaren_P1.mp4</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>Yamaha YZF-R1M</t>
+          <t>KTM 390 Duke</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha YZF-R1M ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature KTM 390 Duke ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
@@ -6678,22 +6678,22 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:51:55</t>
+          <t>2026-09-06 21:12:21</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
+          <t>video-editor\output\17_KTM_390_Duke_master_vehicles_tracker\KTM_390_Duke.mp4</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Mercedes-AMG G63 Brabus 800</t>
+          <t>Dodge Challenger SRT Demon 170</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Miniature Mercedes-AMG G63 Brabus 800 ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Dodge Challenger SRT Demon 170 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -6723,32 +6723,32 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:52:42</t>
+          <t>2026-09-06 23:27:14</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
+          <t>video-editor\output\18_Dodge_Challenger_SRT_Demon_170_master_vehicles_tracker\Dodge_Challenger_SRT_Demon_170.mp4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Bugatti Chiron Super Sport 300+</t>
+          <t>Yamaha YZF-R1M</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Miniature Bugatti Chiron Super Sport 300+ ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Yamaha YZF-R1M ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
@@ -6768,32 +6768,32 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:53:30</t>
+          <t>2026-09-07 02:51:55</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_19_Yamaha_YZF-R1M\Yamaha_YZF-R1M.mp4</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Ninja ZX-10R</t>
+          <t>Mercedes-AMG G63 Brabus 800</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Ninja ZX-10R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Mercedes-AMG G63 Brabus 800 ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -6813,32 +6813,32 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 02:59:11</t>
+          <t>2026-09-07 02:52:42</t>
         </is>
       </c>
       <c r="I141" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_20_Mercedes-AMG_G63_Brabus_800\Mercedes-AMG_G63_Brabus_800.mp4</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Triumph Rocket 3 R</t>
+          <t>Bugatti Chiron Super Sport 300+</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Miniature Triumph Rocket 3 R ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Bugatti Chiron Super Sport 300+ ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
@@ -6858,32 +6858,32 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:17:15</t>
+          <t>2026-09-07 02:53:30</t>
         </is>
       </c>
       <c r="I142" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_21_Bugatti_Chiron_Super_Sport_300+\Bugatti_Chiron_Super_Sport_300+.mp4</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Huracan STO</t>
+          <t>Kawasaki Ninja ZX-10R</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Huracan STO ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Kawasaki Ninja ZX-10R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -6903,22 +6903,22 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:22:07</t>
+          <t>2026-09-07 02:59:11</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_22_Kawasaki_Ninja_ZX-10R\Kawasaki_Ninja_ZX-10R.mp4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>MV Agusta Superveloce 800</t>
+          <t>Triumph Rocket 3 R</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Miniature MV Agusta Superveloce 800 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Triumph Rocket 3 R ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
@@ -6948,22 +6948,22 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:27:12</t>
+          <t>2026-09-07 13:17:15</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_26_Triumph_Rocket_3_R\Triumph_Rocket_3_R.mp4</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Pagani Huayra BC</t>
+          <t>Lamborghini Huracan STO</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -6973,7 +6973,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>Miniature Pagani Huayra BC ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Lamborghini Huracan STO ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -6993,22 +6993,22 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:32:07</t>
+          <t>2026-09-07 13:22:07</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_27_Lamborghini_Huracan_STO\Lamborghini_Huracan_STO.mp4</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>Aprilia RSV4 Factory 1100</t>
+          <t>MV Agusta Superveloce 800</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7018,7 +7018,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Miniature Aprilia RSV4 Factory 1100 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature MV Agusta Superveloce 800 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -7038,22 +7038,22 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 13:36:57</t>
+          <t>2026-09-07 13:27:12</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_28_MV_Agusta_Superveloce_800\MV_Agusta_Superveloce_800.mp4</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Chevrolet Corvette Z06 (C8)</t>
+          <t>Pagani Huayra BC</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>Miniature Chevrolet Corvette Z06 (C8) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Pagani Huayra BC ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:23:04</t>
+          <t>2026-09-07 13:32:07</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_29_Pagani_Huayra_BC\Pagani_Huayra_BC.mp4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>Honda CBR1000RR-R Fireblade SP</t>
+          <t>Aprilia RSV4 Factory 1100</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CBR1000RR-R Fireblade SP ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Aprilia RSV4 Factory 1100 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
@@ -7128,22 +7128,22 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:28:58</t>
+          <t>2026-09-07 13:36:57</t>
         </is>
       </c>
       <c r="I148" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_30_Aprilia_RSV4_Factory_1100\Aprilia_RSV4_Factory_1100.mp4</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>Nissan GT-R Nismo (R35)</t>
+          <t>Chevrolet Corvette Z06 (C8)</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Miniature Nissan GT-R Nismo (R35) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Chevrolet Corvette Z06 (C8) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -7173,22 +7173,22 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 14:31:30</t>
+          <t>2026-09-07 14:23:04</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_31_Chevrolet_Corvette_Z06_(C8)\Chevrolet_Corvette_Z06_(C8).mp4</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>BMW M1000RR</t>
+          <t>Honda CBR1000RR-R Fireblade SP</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Miniature BMW M1000RR ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Honda CBR1000RR-R Fireblade SP ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
@@ -7218,22 +7218,22 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:50:24</t>
+          <t>2026-09-07 14:28:58</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_32_Honda_CBR1000RR-R_Fireblade_SP\Honda_CBR1000RR-R_Fireblade_SP.mp4</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>Ferrari LaFerrari</t>
+          <t>Nissan GT-R Nismo (R35)</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ferrari LaFerrari ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Nissan GT-R Nismo (R35) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -7263,22 +7263,22 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 15:58:43</t>
+          <t>2026-09-07 14:31:30</t>
         </is>
       </c>
       <c r="I151" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_33_Nissan_GT-R_Nismo_(R35)\Nissan_GT-R_Nismo_(R35).mp4</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>KTM 1290 Super Duke R Evo</t>
+          <t>BMW M1000RR</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Miniature KTM 1290 Super Duke R Evo ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature BMW M1000RR ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
@@ -7308,22 +7308,22 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:14:49</t>
+          <t>2026-09-07 15:50:24</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_34_BMW_M1000RR\BMW_M1000RR.mp4</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>Porsche 918 Spyder</t>
+          <t>Ferrari LaFerrari</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>Miniature Porsche 918 Spyder ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Ferrari LaFerrari ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -7353,22 +7353,22 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:25:34</t>
+          <t>2026-09-07 15:58:43</t>
         </is>
       </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_35_Ferrari_LaFerrari\Ferrari_LaFerrari.mp4</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>Harley-Davidson Sportster S</t>
+          <t>KTM 1290 Super Duke R Evo</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Miniature Harley-Davidson Sportster S ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature KTM 1290 Super Duke R Evo ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
@@ -7398,22 +7398,22 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:59:19</t>
+          <t>2026-09-07 21:14:49</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_36_KTM_1290_Super_Duke_R_Evo\KTM_1290_Super_Duke_R_Evo.mp4</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>Shelby Cobra 427 S/C</t>
+          <t>Porsche 918 Spyder</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>Miniature Shelby Cobra 427 S/C ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Porsche 918 Spyder ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -7443,22 +7443,22 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:00:12</t>
+          <t>2026-09-07 21:25:34</t>
         </is>
       </c>
       <c r="I155" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_37_Porsche_918_Spyder\Porsche_918_Spyder.mp4</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>Ducati Diavel V4</t>
+          <t>Harley-Davidson Sportster S</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Miniature Ducati Diavel V4 ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Harley-Davidson Sportster S ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -7488,22 +7488,22 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:00:58</t>
+          <t>2026-09-07 21:59:19</t>
         </is>
       </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_38_Harley-Davidson_Sportster_S\Harley-Davidson_Sportster_S.mp4</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>Audi R8 V10 Performance</t>
+          <t>Shelby Cobra 427 S/C</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Miniature Audi R8 V10 Performance ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Shelby Cobra 427 S/C ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -7533,22 +7533,22 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:01:43</t>
+          <t>2026-09-07 22:00:12</t>
         </is>
       </c>
       <c r="I157" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_39_Shelby_Cobra_427_S_C\Shelby_Cobra_427_S_C.mp4</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>Yamaha MT-10 SP</t>
+          <t>Ducati Diavel V4</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Miniature Yamaha MT-10 SP ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Ducati Diavel V4 ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
@@ -7578,22 +7578,22 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:02:31</t>
+          <t>2026-09-07 22:00:58</t>
         </is>
       </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_40_Ducati_Diavel_V4\Ducati_Diavel_V4.mp4</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Mazda RX-7 Spirit R (FD3S)</t>
+          <t>Audi R8 V10 Performance</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>Miniature Mazda RX-7 Spirit R (FD3S) ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Audi R8 V10 Performance ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -7623,22 +7623,22 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:04:41</t>
+          <t>2026-09-07 22:01:43</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_41_Audi_R8_V10_Performance\Audi_R8_V10_Performance.mp4</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>Kawasaki Z H2 Supercharged</t>
+          <t>Yamaha MT-10 SP</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Miniature Kawasaki Z H2 Supercharged ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Yamaha MT-10 SP ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:05:26</t>
+          <t>2026-09-07 22:02:31</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_42_Yamaha_MT-10_SP\Yamaha_MT-10_SP.mp4</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>Lexus LFA Nurburgring Edition</t>
+          <t>Mazda RX-7 Spirit R (FD3S)</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lexus LFA Nurburgring Edition ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Mazda RX-7 Spirit R (FD3S) ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -7713,22 +7713,22 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:06:21</t>
+          <t>2026-09-07 22:04:41</t>
         </is>
       </c>
       <c r="I161" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_43_Mazda_RX-7_Spirit_R_(FD3S)\Mazda_RX-7_Spirit_R_(FD3S).mp4</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Suzuki Katana</t>
+          <t>Kawasaki Z H2 Supercharged</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Miniature Suzuki Katana ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Kawasaki Z H2 Supercharged ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
@@ -7758,22 +7758,22 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:07:11</t>
+          <t>2026-09-07 22:05:26</t>
         </is>
       </c>
       <c r="I162" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_44_Kawasaki_Z_H2_Supercharged\Kawasaki_Z_H2_Supercharged.mp4</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>McLaren 720S Spider</t>
+          <t>Lexus LFA Nurburgring Edition</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Miniature McLaren 720S Spider ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature Lexus LFA Nurburgring Edition ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -7803,22 +7803,22 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:07:58</t>
+          <t>2026-09-07 22:06:21</t>
         </is>
       </c>
       <c r="I163" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_45_Lexus_LFA_Nurburgring_Edition\Lexus_LFA_Nurburgring_Edition.mp4</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>Honda CB1000R Black Edition</t>
+          <t>Suzuki Katana</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Miniature Honda CB1000R Black Edition ASMR Unboxing 🏍️ #shorts #bikes</t>
+          <t>Miniature Suzuki Katana ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
@@ -7848,22 +7848,22 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:32:57</t>
+          <t>2026-09-07 22:07:11</t>
         </is>
       </c>
       <c r="I164" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_46_Suzuki_Katana\Suzuki_Katana.mp4</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>Lamborghini Murcielago LP670-4 SV</t>
+          <t>McLaren 720S Spider</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>Miniature Lamborghini Murcielago LP670-4 SV ASMR Unboxing 🏎️ #shorts #cars</t>
+          <t>Miniature McLaren 720S Spider ASMR Unboxing 🏎️ #shorts #cars</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -7893,55 +7893,145 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-07 22:33:48</t>
+          <t>2026-09-07 22:07:58</t>
         </is>
       </c>
       <c r="I165" s="3" t="inlineStr">
         <is>
-          <t>video-editor\output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+          <t>video-editor\output\master_vehicles_tracker_47_McLaren_720S_Spider\McLaren_720S_Spider.mp4</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>Honda CB1000R Black Edition</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Honda CB1000R Black Edition ASMR Unboxing 🏍️ #shorts #bikes</t>
+        </is>
+      </c>
+      <c r="E166" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:32:57</t>
+        </is>
+      </c>
+      <c r="I166" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_48_Honda_CB1000R_Black_Edition\Honda_CB1000R_Black_Edition.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>Lamborghini Murcielago LP670-4 SV</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Miniature Lamborghini Murcielago LP670-4 SV ASMR Unboxing 🏎️ #shorts #cars</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:33:48</t>
+        </is>
+      </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>video-editor\output\master_vehicles_tracker_49_Lamborghini_Murcielago_LP670-4_SV\Lamborghini_Murcielago_LP670-4_SV.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="B166" s="3" t="inlineStr">
+      <c r="B168" s="3" t="inlineStr">
         <is>
           <t>Indian Scout Bobber</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
         <is>
           <t>Motorcycle</t>
         </is>
       </c>
-      <c r="D166" s="3" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>Miniature Indian Scout Bobber ASMR Unboxing 🏍️ #shorts #bikes</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>https://studio.youtube.com/channel/videos/short</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>PUBLIC</t>
-        </is>
-      </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>UPLOADED</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>https://studio.youtube.com/channel/videos/short</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>PUBLIC</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>UPLOADED</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>2026-09-07 22:34:33</t>
         </is>
       </c>
-      <c r="I166" s="3" t="inlineStr">
+      <c r="I168" s="3" t="inlineStr">
         <is>
           <t>video-editor\output\master_vehicles_tracker_50_Indian_Scout_Bobber\Indian_Scout_Bobber.mp4</t>
         </is>
@@ -8114,6 +8204,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
